--- a/Result/profitability/4160.xlsx
+++ b/Result/profitability/4160.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2275</v>
+        <v>0.16625</v>
       </c>
       <c r="N2" t="n">
-        <v>38.02875</v>
+        <v>37.74875</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0.225</v>
+        <v>0.23875</v>
       </c>
       <c r="N3" t="n">
-        <v>39.7275</v>
+        <v>39.96875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -8566,6 +8566,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4160</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>150</v>
+      </c>
+      <c r="D65" t="n">
+        <v>88</v>
+      </c>
+      <c r="E65" t="n">
+        <v>63</v>
+      </c>
+      <c r="F65" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4</v>
+      </c>
+      <c r="K65" t="n">
+        <v>6</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.23625</v>
+      </c>
+      <c r="N65" t="n">
+        <v>41.46875</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X65" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.350000000000001</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.03344895936570857</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.140000000000001</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.02809958097116105</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
